--- a/Tests/CSCS_Frontend_Test_Suite.xlsx
+++ b/Tests/CSCS_Frontend_Test_Suite.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/achrafcheniti/Documents/Summer_2026/COMP 353/cscs-db-353/Tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5667F3F4-58DC-EE4E-B02D-17737EE7CD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31931B10-26E6-4E42-81B7-7354E0757C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="220">
   <si>
     <t>CSCS Main Project — Frontend Constraint Test Plan</t>
   </si>
@@ -713,6 +713,82 @@
   </si>
   <si>
     <t>Pass rate (of executed tests)</t>
+  </si>
+  <si>
+    <t>Achraf</t>
+  </si>
+  <si>
+    <t>15-08-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The club can only have one Head location.
+</t>
+  </si>
+  <si>
+    <t>No Issue you can create a branch</t>
+  </si>
+  <si>
+    <t>The club can only have one Head location.
+This works fine</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We need to create a section to preview the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">PersonnelAssignment.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">This trigger requires a section in the Personnel page trg_personnel_assignment_before_insert Which must be implement in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>frontend</t>
+    </r>
+  </si>
+  <si>
+    <t>Same note as the one above</t>
+  </si>
+  <si>
+    <t>We need to create a section to preview the FamilyMemberAssignment Similar to the PersonnelAssignment</t>
+  </si>
+  <si>
+    <t>You can only leave at least one family member for those under 18 years old</t>
+  </si>
+  <si>
+    <t>As long as you have one relation and the member &lt; 18 all is good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cannot update this family relation: a minor club member must always have at least one active linked family member.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A club member must have been at least 4 years old at registration.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location capacity reached: another active club member cannot be added.
+</t>
+  </si>
+  <si>
+    <t>Works fine</t>
   </si>
 </sst>
 </file>
@@ -722,7 +798,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -735,48 +811,54 @@
       <sz val="16"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -842,10 +924,6 @@
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -886,6 +964,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1184,130 +1266,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="28" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="28" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="28" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="28" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="28" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="1"/>
+      <c r="B20" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1336,1031 +1418,1099 @@
     <col min="7" max="7" width="26" customWidth="1"/>
     <col min="8" max="9" width="40" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="11" max="11" width="29.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="6">
         <v>1</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="9">
+        <v>2</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="6">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="98" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="9">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+    </row>
+    <row r="6" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="6">
+        <v>2</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+    </row>
+    <row r="7" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="6">
+        <v>2</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="6">
+        <v>3</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="9">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="9">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="6">
+        <v>2</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="9">
+        <v>2</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="6">
+        <v>2</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-    </row>
-    <row r="3" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="11">
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+    </row>
+    <row r="17" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" s="9">
+        <v>1</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+    </row>
+    <row r="18" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+    </row>
+    <row r="19" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" s="9">
+        <v>1</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+    </row>
+    <row r="20" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+    </row>
+    <row r="21" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21" s="9">
+        <v>1</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+    </row>
+    <row r="22" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D23" s="9">
         <v>2</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E23" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="J3" s="10" t="s">
+      <c r="F23" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-    </row>
-    <row r="4" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="8">
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+    </row>
+    <row r="24" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D24" s="6">
         <v>2</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E24" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="J4" s="10" t="s">
+      <c r="F24" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-    </row>
-    <row r="5" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="11">
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+    </row>
+    <row r="25" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D25" s="9">
         <v>1</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E25" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J5" s="10" t="s">
+      <c r="F25" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-    </row>
-    <row r="6" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="8">
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+    </row>
+    <row r="26" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D26" s="6">
         <v>2</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E26" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="J6" s="10" t="s">
+      <c r="F26" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-    </row>
-    <row r="7" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="11">
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+    </row>
+    <row r="27" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D27" s="9">
         <v>1</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E27" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="J7" s="10" t="s">
+      <c r="F27" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-    </row>
-    <row r="8" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="8">
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+    </row>
+    <row r="28" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D28" s="6">
         <v>2</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E28" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+    </row>
+    <row r="29" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D29" s="9">
+        <v>2</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="J8" s="10" t="s">
+      <c r="F29" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-    </row>
-    <row r="9" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" s="11">
-        <v>1</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-    </row>
-    <row r="10" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="8">
-        <v>3</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-    </row>
-    <row r="11" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" s="11">
-        <v>2</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-    </row>
-    <row r="12" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="8">
-        <v>1</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-    </row>
-    <row r="13" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" s="11">
-        <v>1</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-    </row>
-    <row r="14" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" s="8">
-        <v>2</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-    </row>
-    <row r="15" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D15" s="11">
-        <v>2</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-    </row>
-    <row r="16" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="D16" s="8">
-        <v>2</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-    </row>
-    <row r="17" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D17" s="11">
-        <v>1</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-    </row>
-    <row r="18" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D18" s="8">
-        <v>1</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-    </row>
-    <row r="19" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D19" s="11">
-        <v>1</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-    </row>
-    <row r="20" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D20" s="8">
-        <v>1</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-    </row>
-    <row r="21" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="D21" s="11">
-        <v>1</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-    </row>
-    <row r="22" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D22" s="8">
-        <v>1</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-    </row>
-    <row r="23" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="D23" s="11">
-        <v>2</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-    </row>
-    <row r="24" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D24" s="8">
-        <v>2</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-    </row>
-    <row r="25" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="D25" s="11">
-        <v>1</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-    </row>
-    <row r="26" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D26" s="8">
-        <v>2</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-    </row>
-    <row r="27" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="D27" s="11">
-        <v>1</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-    </row>
-    <row r="28" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="D28" s="8">
-        <v>2</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-    </row>
-    <row r="29" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="D29" s="11">
-        <v>2</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M29" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
@@ -2399,242 +2549,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="12">
         <f>COUNTIF('Test Cases'!$B$2:$B$29,A4)</f>
         <v>3</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A4,'Test Cases'!$J$2:$J$29,"Passed")</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="14">
+        <v>3</v>
+      </c>
+      <c r="D4" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A4,'Test Cases'!$J$2:$J$29,"Failed")</f>
         <v>0</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A4,'Test Cases'!$J$2:$J$29,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A4,'Test Cases'!$J$2:$J$29,"Not Run")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="12">
         <f>COUNTIF('Test Cases'!$B$2:$B$29,A5)</f>
         <v>2</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A5,'Test Cases'!$J$2:$J$29,"Passed")</f>
         <v>0</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A5,'Test Cases'!$J$2:$J$29,"Failed")</f>
         <v>0</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A5,'Test Cases'!$J$2:$J$29,"Blocked")</f>
+        <v>2</v>
+      </c>
+      <c r="F5" s="12">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$29,A5,'Test Cases'!$J$2:$J$29,"Not Run")</f>
         <v>0</v>
       </c>
-      <c r="F5" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$29,A5,'Test Cases'!$J$2:$J$29,"Not Run")</f>
-        <v>2</v>
-      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="12">
         <f>COUNTIF('Test Cases'!$B$2:$B$29,A6)</f>
         <v>5</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A6,'Test Cases'!$J$2:$J$29,"Passed")</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="14">
+        <v>3</v>
+      </c>
+      <c r="D6" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A6,'Test Cases'!$J$2:$J$29,"Failed")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A6,'Test Cases'!$J$2:$J$29,"Blocked")</f>
+        <v>2</v>
+      </c>
+      <c r="F6" s="12">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$29,A6,'Test Cases'!$J$2:$J$29,"Not Run")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$29,A6,'Test Cases'!$J$2:$J$29,"Not Run")</f>
-        <v>5</v>
-      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="12">
         <f>COUNTIF('Test Cases'!$B$2:$B$29,A7)</f>
         <v>4</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A7,'Test Cases'!$J$2:$J$29,"Passed")</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="14">
+        <v>4</v>
+      </c>
+      <c r="D7" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A7,'Test Cases'!$J$2:$J$29,"Failed")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A7,'Test Cases'!$J$2:$J$29,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A7,'Test Cases'!$J$2:$J$29,"Not Run")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="12">
         <f>COUNTIF('Test Cases'!$B$2:$B$29,A8)</f>
         <v>4</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A8,'Test Cases'!$J$2:$J$29,"Passed")</f>
         <v>0</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A8,'Test Cases'!$J$2:$J$29,"Failed")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A8,'Test Cases'!$J$2:$J$29,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A8,'Test Cases'!$J$2:$J$29,"Not Run")</f>
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="12">
         <f>COUNTIF('Test Cases'!$B$2:$B$29,A9)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A9,'Test Cases'!$J$2:$J$29,"Passed")</f>
         <v>0</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A9,'Test Cases'!$J$2:$J$29,"Failed")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A9,'Test Cases'!$J$2:$J$29,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A9,'Test Cases'!$J$2:$J$29,"Not Run")</f>
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="12">
         <f>COUNTIF('Test Cases'!$B$2:$B$29,A10)</f>
         <v>3</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A10,'Test Cases'!$J$2:$J$29,"Passed")</f>
         <v>0</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A10,'Test Cases'!$J$2:$J$29,"Failed")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A10,'Test Cases'!$J$2:$J$29,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A10,'Test Cases'!$J$2:$J$29,"Not Run")</f>
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="14">
         <f>SUM(B4:B10)</f>
         <v>28</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="14">
         <f>SUM(C4:C10)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="16">
+        <v>10</v>
+      </c>
+      <c r="D11" s="14">
         <f>SUM(D4:D10)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="14">
         <f>SUM(E4:E10)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="16">
+        <v>4</v>
+      </c>
+      <c r="F11" s="14">
         <f>SUM(F4:F10)</f>
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B13" s="17" t="str">
+      <c r="B13" s="15">
         <f>IFERROR(C11/(C11+D11+E11),"n/a")</f>
-        <v>n/a</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
   </sheetData>

--- a/Tests/CSCS_Frontend_Test_Suite.xlsx
+++ b/Tests/CSCS_Frontend_Test_Suite.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/achrafcheniti/Documents/Summer_2026/COMP 353/cscs-db-353/Tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31931B10-26E6-4E42-81B7-7354E0757C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3F7492-9D7C-EF42-8084-6C75FF872B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="226">
   <si>
     <t>CSCS Main Project — Frontend Constraint Test Plan</t>
   </si>
@@ -789,6 +789,28 @@
   </si>
   <si>
     <t>Works fine</t>
+  </si>
+  <si>
+    <t>Record added successfully</t>
+  </si>
+  <si>
+    <t>16-08-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both team formations in a session must be the same category (Boys or Girls).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A session can contain exactly two team formations; a third formation is not allowed.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Club member location does not match the team formation location.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Club member gender does not match the team formation category.
+</t>
   </si>
 </sst>
 </file>
@@ -2051,11 +2073,17 @@
         <v>132</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
+        <v>201</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="17" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
@@ -2086,11 +2114,17 @@
         <v>137</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
+        <v>201</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="18" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
@@ -2121,11 +2155,17 @@
         <v>141</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
+        <v>201</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="19" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
@@ -2156,11 +2196,17 @@
         <v>146</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
+        <v>201</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="20" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
@@ -2191,11 +2237,17 @@
         <v>153</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
+        <v>201</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="21" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
@@ -2226,13 +2278,19 @@
         <v>158</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-    </row>
-    <row r="22" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>201</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="70" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>159</v>
       </c>
@@ -2688,7 +2746,7 @@
       </c>
       <c r="C8" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A8,'Test Cases'!$J$2:$J$29,"Passed")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A8,'Test Cases'!$J$2:$J$29,"Failed")</f>
@@ -2700,7 +2758,7 @@
       </c>
       <c r="F8" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A8,'Test Cases'!$J$2:$J$29,"Not Run")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -2713,7 +2771,7 @@
       </c>
       <c r="C9" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A9,'Test Cases'!$J$2:$J$29,"Passed")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A9,'Test Cases'!$J$2:$J$29,"Failed")</f>
@@ -2725,7 +2783,7 @@
       </c>
       <c r="F9" s="12">
         <f>COUNTIFS('Test Cases'!$B$2:$B$29,A9,'Test Cases'!$J$2:$J$29,"Not Run")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -2763,7 +2821,7 @@
       </c>
       <c r="C11" s="14">
         <f>SUM(C4:C10)</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D11" s="14">
         <f>SUM(D4:D10)</f>
@@ -2775,7 +2833,7 @@
       </c>
       <c r="F11" s="14">
         <f>SUM(F4:F10)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -2784,7 +2842,7 @@
       </c>
       <c r="B13" s="15">
         <f>IFERROR(C11/(C11+D11+E11),"n/a")</f>
-        <v>0.7142857142857143</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
